--- a/HG AMD生産計画 2026.10.10.xlsx
+++ b/HG AMD生産計画 2026.10.10.xlsx
@@ -752,7 +752,7 @@
         <v>2026-08-20T00:00:00.000Z</v>
       </c>
       <c r="H12" t="str" s="2">
-        <v>ARM</v>
+        <v>B&amp;R ARM</v>
       </c>
     </row>
     <row r="13">
@@ -1012,7 +1012,7 @@
         <v>2026-09-08T00:00:00.000Z</v>
       </c>
       <c r="H22" t="str" s="2">
-        <v>ARM</v>
+        <v>B&amp;R ARM</v>
       </c>
     </row>
     <row r="23">
@@ -1402,7 +1402,7 @@
         <v>2026-10-23T00:00:00.000Z</v>
       </c>
       <c r="H37" t="str" s="2">
-        <v>ARM</v>
+        <v>B&amp;R ARM</v>
       </c>
     </row>
     <row r="38">

--- a/HG AMD生産計画 2026.10.10.xlsx
+++ b/HG AMD生産計画 2026.10.10.xlsx
@@ -440,7 +440,7 @@
     <col min="5" max="5" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="51.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
         <v>2026-07-17T00:00:00.000Z</v>
       </c>
       <c r="H4" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="5">
@@ -830,7 +830,7 @@
         <v>2026-08-25T00:00:00.000Z</v>
       </c>
       <c r="H15" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="16">
@@ -908,7 +908,7 @@
         <v>2026-09-02T00:00:00.000Z</v>
       </c>
       <c r="H18" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="19">
@@ -1558,7 +1558,7 @@
         <v>2026-11-04T00:00:00.000Z</v>
       </c>
       <c r="H43" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="44">
@@ -1740,7 +1740,7 @@
         <v>2026-11-19T00:00:00.000Z</v>
       </c>
       <c r="H50" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="51">
@@ -1948,7 +1948,7 @@
         <v>2026-12-05T00:00:00.000Z</v>
       </c>
       <c r="H58" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="59">
@@ -1974,7 +1974,7 @@
         <v>2026-12-09T00:00:00.000Z</v>
       </c>
       <c r="H59" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="60">
@@ -2052,7 +2052,7 @@
         <v>2026-12-12T00:00:00.000Z</v>
       </c>
       <c r="H62" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="63">
@@ -2208,7 +2208,7 @@
         <v>2026-12-26T00:00:00.000Z</v>
       </c>
       <c r="H68" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="69">
@@ -2338,7 +2338,7 @@
         <v>2027-01-13T00:00:00.000Z</v>
       </c>
       <c r="H73" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="74">
@@ -2390,7 +2390,7 @@
         <v>2027-01-15T00:00:00.000Z</v>
       </c>
       <c r="H75" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="76">
@@ -2442,7 +2442,7 @@
         <v>2027-01-20T00:00:00.000Z</v>
       </c>
       <c r="H77" t="str" s="2">
-        <v>ATC</v>
+        <v>Y化 Σ10 ATC</v>
       </c>
     </row>
     <row r="78">

--- a/HG AMD生産計画 2026.10.10.xlsx
+++ b/HG AMD生産計画 2026.10.10.xlsx
@@ -1497,7 +1497,7 @@
         <v>EXP</v>
       </c>
       <c r="E41" t="str" s="2">
-        <v/>
+        <v>米国</v>
       </c>
       <c r="F41" t="str" s="2">
         <v>【AAI】Delta</v>
@@ -1523,7 +1523,7 @@
         <v>EXP</v>
       </c>
       <c r="E42" t="str" s="2">
-        <v/>
+        <v>米国</v>
       </c>
       <c r="F42" t="str" s="2">
         <v>【AAI】Delta</v>
@@ -1575,7 +1575,7 @@
         <v>EXP</v>
       </c>
       <c r="E44" t="str" s="2">
-        <v/>
+        <v>米国</v>
       </c>
       <c r="F44" t="str" s="2">
         <v>【AAI】Delta</v>

--- a/HG AMD生産計画 2026.10.10.xlsx
+++ b/HG AMD生産計画 2026.10.10.xlsx
@@ -925,7 +925,7 @@
         <v>EXP</v>
       </c>
       <c r="E19" t="str" s="2">
-        <v/>
+        <v>カナダ</v>
       </c>
       <c r="F19" t="str" s="2">
         <v>【ACL】Metal Contracting</v>
@@ -1055,7 +1055,7 @@
         <v>EXP</v>
       </c>
       <c r="E24" t="str" s="2">
-        <v/>
+        <v>カナダ</v>
       </c>
       <c r="F24" t="str" s="2">
         <v>【ACL】Bercomac</v>
@@ -2407,7 +2407,7 @@
         <v>EXP</v>
       </c>
       <c r="E76" t="str" s="2">
-        <v/>
+        <v>カナダ</v>
       </c>
       <c r="F76" t="str" s="2">
         <v>【ACL】Greidy Labs</v>

--- a/HG AMD生産計画 2026.10.10.xlsx
+++ b/HG AMD生産計画 2026.10.10.xlsx
@@ -7,7 +7,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'JIT日一覧'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'JIT日一覧'!A1:H87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'JIT日一覧'!A1:G87</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -431,16 +431,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:G87"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="51.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" customWidth="1"/>
+    <col min="5" max="5" width="51.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,18 +453,15 @@
         <v>シリアル</v>
       </c>
       <c r="D1" t="str" s="3">
-        <v>仕向</v>
+        <v>国名</v>
       </c>
       <c r="E1" t="str" s="3">
-        <v>国名</v>
+        <v>客先名</v>
       </c>
       <c r="F1" t="str" s="3">
-        <v>客先名</v>
+        <v>JIT日</v>
       </c>
       <c r="G1" t="str" s="3">
-        <v>JIT日</v>
-      </c>
-      <c r="H1" t="str" s="3">
         <v>備考</v>
       </c>
     </row>
@@ -480,18 +476,15 @@
         <v>22037218</v>
       </c>
       <c r="D2" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E2" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F2" t="str" s="2">
         <v>フジタ自動車工業（株）</v>
       </c>
-      <c r="G2" s="4" t="d">
+      <c r="F2" s="4" t="d">
         <v>2026-07-11T00:00:00.000Z</v>
       </c>
-      <c r="H2" t="str" s="2">
+      <c r="G2" t="str" s="2">
         <v>Y化 Σ7</v>
       </c>
     </row>
@@ -506,18 +499,15 @@
         <v>22468010</v>
       </c>
       <c r="D3" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E3" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F3" t="str" s="2">
         <v>（株）遠藤製作所</v>
       </c>
-      <c r="G3" s="4" t="d">
+      <c r="F3" s="4" t="d">
         <v>2026-07-14T00:00:00.000Z</v>
       </c>
-      <c r="H3" t="str" s="2">
+      <c r="G3" t="str" s="2">
         <v>B&amp;R</v>
       </c>
     </row>
@@ -532,18 +522,15 @@
         <v>22404197</v>
       </c>
       <c r="D4" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E4" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F4" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G4" s="4" t="d">
+      <c r="F4" s="4" t="d">
         <v>2026-07-17T00:00:00.000Z</v>
       </c>
-      <c r="H4" t="str" s="2">
+      <c r="G4" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -558,18 +545,15 @@
         <v>22402951</v>
       </c>
       <c r="D5" t="str" s="2">
-        <v>EXP</v>
+        <v>インド</v>
       </c>
       <c r="E5" t="str" s="2">
-        <v>インド</v>
-      </c>
-      <c r="F5" t="str" s="2">
         <v>【インド】New Era Industries</v>
       </c>
-      <c r="G5" s="4" t="d">
+      <c r="F5" s="4" t="d">
         <v>2026-07-24T00:00:00.000Z</v>
       </c>
-      <c r="H5" t="str" s="2">
+      <c r="G5" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -584,18 +568,15 @@
         <v>22402943</v>
       </c>
       <c r="D6" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E6" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F6" t="str" s="2">
         <v>文化シヤッター（株）</v>
       </c>
-      <c r="G6" s="4" t="d">
+      <c r="F6" s="4" t="d">
         <v>2026-07-24T00:00:00.000Z</v>
       </c>
-      <c r="H6" t="str" s="2">
+      <c r="G6" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -610,18 +591,15 @@
         <v>17302377</v>
       </c>
       <c r="D7" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E7" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F7" t="str" s="2">
         <v>（株）ＮＳＴ</v>
       </c>
-      <c r="G7" s="4" t="d">
+      <c r="F7" s="4" t="d">
         <v>2026-07-31T00:00:00.000Z</v>
       </c>
-      <c r="H7" t="str" s="2">
+      <c r="G7" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -636,18 +614,15 @@
         <v>17302378</v>
       </c>
       <c r="D8" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E8" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F8" t="str" s="2">
         <v>（有）海邦ベンダー工業</v>
       </c>
-      <c r="G8" s="4" t="d">
+      <c r="F8" s="4" t="d">
         <v>2026-07-31T00:00:00.000Z</v>
       </c>
-      <c r="H8" t="str" s="2">
+      <c r="G8" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -662,18 +637,15 @@
         <v>22302236</v>
       </c>
       <c r="D9" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E9" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F9" t="str" s="2">
         <v>（株）ミワレーザー</v>
       </c>
-      <c r="G9" s="4" t="d">
+      <c r="F9" s="4" t="d">
         <v>2026-08-01T00:00:00.000Z</v>
       </c>
-      <c r="H9" t="str" s="2">
+      <c r="G9" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -688,18 +660,15 @@
         <v>22402944</v>
       </c>
       <c r="D10" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E10" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F10" t="str" s="2">
         <v>（株）アマダベンディングＳ部</v>
       </c>
-      <c r="G10" s="4" t="d">
+      <c r="F10" s="4" t="d">
         <v>2026-08-07T00:00:00.000Z</v>
       </c>
-      <c r="H10" t="str" s="2">
+      <c r="G10" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -714,18 +683,15 @@
         <v>22402945</v>
       </c>
       <c r="D11" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E11" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F11" t="str" s="2">
         <v>（株）明豊</v>
       </c>
-      <c r="G11" s="4" t="d">
+      <c r="F11" s="4" t="d">
         <v>2026-08-07T00:00:00.000Z</v>
       </c>
-      <c r="H11" t="str" s="2">
+      <c r="G11" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -740,18 +706,15 @@
         <v>22448035</v>
       </c>
       <c r="D12" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E12" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F12" t="str" s="2">
         <v>（株）徹工業</v>
       </c>
-      <c r="G12" s="4" t="d">
+      <c r="F12" s="4" t="d">
         <v>2026-08-20T00:00:00.000Z</v>
       </c>
-      <c r="H12" t="str" s="2">
+      <c r="G12" t="str" s="2">
         <v>B&amp;R ARM</v>
       </c>
     </row>
@@ -766,18 +729,15 @@
         <v>22302244</v>
       </c>
       <c r="D13" t="str" s="2">
-        <v>EXP</v>
+        <v>韓国</v>
       </c>
       <c r="E13" t="str" s="2">
-        <v>韓国</v>
-      </c>
-      <c r="F13" t="str" s="2">
         <v>ＡＭＡＤＡ　ＫＯＲＥＡ　ＣＯ．，ＬＴＤ．</v>
       </c>
-      <c r="G13" s="4" t="d">
+      <c r="F13" s="4" t="d">
         <v>2026-08-20T00:00:00.000Z</v>
       </c>
-      <c r="H13" t="str" s="2">
+      <c r="G13" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -792,18 +752,15 @@
         <v>22402946</v>
       </c>
       <c r="D14" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E14" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F14" t="str" s="2">
         <v>ナブコアール（株）</v>
       </c>
-      <c r="G14" s="4" t="d">
+      <c r="F14" s="4" t="d">
         <v>2026-08-25T00:00:00.000Z</v>
       </c>
-      <c r="H14" t="str" s="2">
+      <c r="G14" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -818,18 +775,15 @@
         <v>22404200</v>
       </c>
       <c r="D15" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E15" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F15" t="str" s="2">
         <v>安田技研（株）</v>
       </c>
-      <c r="G15" s="4" t="d">
+      <c r="F15" s="4" t="d">
         <v>2026-08-25T00:00:00.000Z</v>
       </c>
-      <c r="H15" t="str" s="2">
+      <c r="G15" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -844,18 +798,15 @@
         <v>22402954</v>
       </c>
       <c r="D16" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E16" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F16" t="str" s="2">
         <v>ＡＭＡＤＡ　ＣＡＮＡＤＡ　ＬＴＤ．</v>
       </c>
-      <c r="G16" s="4" t="d">
+      <c r="F16" s="4" t="d">
         <v>2026-08-28T00:00:00.000Z</v>
       </c>
-      <c r="H16" t="str" s="2">
+      <c r="G16" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -870,18 +821,15 @@
         <v>22402956</v>
       </c>
       <c r="D17" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E17" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F17" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G17" s="4" t="d">
+      <c r="F17" s="4" t="d">
         <v>2026-08-28T00:00:00.000Z</v>
       </c>
-      <c r="H17" t="str" s="2">
+      <c r="G17" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -896,18 +844,15 @@
         <v>22404195</v>
       </c>
       <c r="D18" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E18" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F18" t="str" s="2">
         <v>（株）廣澤精機製作所</v>
       </c>
-      <c r="G18" s="4" t="d">
+      <c r="F18" s="4" t="d">
         <v>2026-09-02T00:00:00.000Z</v>
       </c>
-      <c r="H18" t="str" s="2">
+      <c r="G18" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -922,18 +867,15 @@
         <v>22402952</v>
       </c>
       <c r="D19" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E19" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F19" t="str" s="2">
         <v>【ACL】Metal Contracting</v>
       </c>
-      <c r="G19" s="4" t="d">
+      <c r="F19" s="4" t="d">
         <v>2026-09-02T00:00:00.000Z</v>
       </c>
-      <c r="H19" t="str" s="2">
+      <c r="G19" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -948,18 +890,15 @@
         <v>17302379</v>
       </c>
       <c r="D20" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E20" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F20" t="str" s="2">
         <v>（株）ＴＩＳＭ</v>
       </c>
-      <c r="G20" s="4" t="d">
+      <c r="F20" s="4" t="d">
         <v>2026-09-04T00:00:00.000Z</v>
       </c>
-      <c r="H20" t="str" s="2">
+      <c r="G20" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -974,18 +913,15 @@
         <v>22402955</v>
       </c>
       <c r="D21" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E21" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F21" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G21" s="4" t="d">
+      <c r="F21" s="4" t="d">
         <v>2026-09-04T00:00:00.000Z</v>
       </c>
-      <c r="H21" t="str" s="2">
+      <c r="G21" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1000,18 +936,15 @@
         <v>22448034</v>
       </c>
       <c r="D22" t="str" s="2">
-        <v>EXP</v>
+        <v>ブラジル</v>
       </c>
       <c r="E22" t="str" s="2">
-        <v>ブラジル</v>
-      </c>
-      <c r="F22" t="str" s="2">
         <v>【ブラジル】PERTO</v>
       </c>
-      <c r="G22" s="4" t="d">
+      <c r="F22" s="4" t="d">
         <v>2026-09-08T00:00:00.000Z</v>
       </c>
-      <c r="H22" t="str" s="2">
+      <c r="G22" t="str" s="2">
         <v>B&amp;R ARM</v>
       </c>
     </row>
@@ -1026,18 +959,15 @@
         <v>22402947</v>
       </c>
       <c r="D23" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E23" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F23" t="str" s="2">
         <v>（株）廣澤精機製作所</v>
       </c>
-      <c r="G23" s="4" t="d">
+      <c r="F23" s="4" t="d">
         <v>2026-09-11T00:00:00.000Z</v>
       </c>
-      <c r="H23" t="str" s="2">
+      <c r="G23" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1052,18 +982,15 @@
         <v>17302381</v>
       </c>
       <c r="D24" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E24" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F24" t="str" s="2">
         <v>【ACL】Bercomac</v>
       </c>
-      <c r="G24" s="4" t="d">
+      <c r="F24" s="4" t="d">
         <v>2026-09-11T00:00:00.000Z</v>
       </c>
-      <c r="H24" t="str" s="2">
+      <c r="G24" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1078,18 +1005,15 @@
         <v>22302245</v>
       </c>
       <c r="D25" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E25" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F25" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G25" s="4" t="d">
+      <c r="F25" s="4" t="d">
         <v>2026-09-12T00:00:00.000Z</v>
       </c>
-      <c r="H25" t="str" s="2">
+      <c r="G25" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1104,18 +1028,15 @@
         <v>17402207</v>
       </c>
       <c r="D26" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E26" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F26" t="str" s="2">
         <v>（株）平島</v>
       </c>
-      <c r="G26" s="4" t="d">
+      <c r="F26" s="4" t="d">
         <v>2026-09-15T00:00:00.000Z</v>
       </c>
-      <c r="H26" t="str" s="2">
+      <c r="G26" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1130,18 +1051,15 @@
         <v>22402957</v>
       </c>
       <c r="D27" t="str" s="2">
-        <v>EXP</v>
+        <v/>
       </c>
       <c r="E27" t="str" s="2">
-        <v/>
-      </c>
-      <c r="F27" t="str" s="2">
         <v>Bao Tien Industrial Company</v>
       </c>
-      <c r="G27" s="4" t="d">
+      <c r="F27" s="4" t="d">
         <v>2026-09-15T00:00:00.000Z</v>
       </c>
-      <c r="H27" t="str" s="2">
+      <c r="G27" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1156,18 +1074,15 @@
         <v>22402961</v>
       </c>
       <c r="D28" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E28" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F28" t="str" s="2">
         <v>（株）アマダベンディングＳ部</v>
       </c>
-      <c r="G28" s="4" t="d">
+      <c r="F28" s="4" t="d">
         <v>2026-09-25T00:00:00.000Z</v>
       </c>
-      <c r="H28" t="str" s="2">
+      <c r="G28" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1182,18 +1097,15 @@
         <v>22402962</v>
       </c>
       <c r="D29" t="str" s="2">
-        <v>EXP</v>
+        <v>中国</v>
       </c>
       <c r="E29" t="str" s="2">
-        <v>中国</v>
-      </c>
-      <c r="F29" t="str" s="2">
         <v>【CHINA】Delta</v>
       </c>
-      <c r="G29" s="4" t="d">
+      <c r="F29" s="4" t="d">
         <v>2026-09-30T00:00:00.000Z</v>
       </c>
-      <c r="H29" t="str" s="2">
+      <c r="G29" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1208,18 +1120,15 @@
         <v>22402963</v>
       </c>
       <c r="D30" t="str" s="2">
-        <v>EXP</v>
+        <v>中国</v>
       </c>
       <c r="E30" t="str" s="2">
-        <v>中国</v>
-      </c>
-      <c r="F30" t="str" s="2">
         <v>【CHINA】Delta</v>
       </c>
-      <c r="G30" s="4" t="d">
+      <c r="F30" s="4" t="d">
         <v>2026-09-30T00:00:00.000Z</v>
       </c>
-      <c r="H30" t="str" s="2">
+      <c r="G30" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1234,18 +1143,15 @@
         <v>22302246</v>
       </c>
       <c r="D31" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E31" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F31" t="str" s="2">
         <v>ＩＭＣ（株）</v>
       </c>
-      <c r="G31" s="4" t="d">
+      <c r="F31" s="4" t="d">
         <v>2026-10-02T00:00:00.000Z</v>
       </c>
-      <c r="H31" t="str" s="2">
+      <c r="G31" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1260,18 +1166,15 @@
         <v>22302247</v>
       </c>
       <c r="D32" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E32" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F32" t="str" s="2">
         <v>（株）シンコー</v>
       </c>
-      <c r="G32" s="4" t="d">
+      <c r="F32" s="4" t="d">
         <v>2026-10-02T00:00:00.000Z</v>
       </c>
-      <c r="H32" t="str" s="2">
+      <c r="G32" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1286,18 +1189,15 @@
         <v>17302383</v>
       </c>
       <c r="D33" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E33" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F33" t="str" s="2">
         <v>（株）日立アイイーシステム</v>
       </c>
-      <c r="G33" s="4" t="d">
+      <c r="F33" s="4" t="d">
         <v>2026-10-10T00:00:00.000Z</v>
       </c>
-      <c r="H33" t="str" s="2">
+      <c r="G33" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1312,18 +1212,15 @@
         <v>22402969</v>
       </c>
       <c r="D34" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E34" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F34" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G34" s="4" t="d">
+      <c r="F34" s="4" t="d">
         <v>2026-10-10T00:00:00.000Z</v>
       </c>
-      <c r="H34" t="str" s="2">
+      <c r="G34" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1338,18 +1235,15 @@
         <v>22402970</v>
       </c>
       <c r="D35" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E35" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F35" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G35" s="4" t="d">
+      <c r="F35" s="4" t="d">
         <v>2026-10-14T00:00:00.000Z</v>
       </c>
-      <c r="H35" t="str" s="2">
+      <c r="G35" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1364,18 +1258,15 @@
         <v>22402971</v>
       </c>
       <c r="D36" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E36" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F36" t="str" s="2">
         <v>ＡＭＡＤＡ　ＣＡＮＡＤＡ　ＬＴＤ．</v>
       </c>
-      <c r="G36" s="4" t="d">
+      <c r="F36" s="4" t="d">
         <v>2026-10-14T00:00:00.000Z</v>
       </c>
-      <c r="H36" t="str" s="2">
+      <c r="G36" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1390,18 +1281,15 @@
         <v>22448036</v>
       </c>
       <c r="D37" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E37" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F37" t="str" s="2">
         <v>（株）徹工業</v>
       </c>
-      <c r="G37" s="4" t="d">
+      <c r="F37" s="4" t="d">
         <v>2026-10-23T00:00:00.000Z</v>
       </c>
-      <c r="H37" t="str" s="2">
+      <c r="G37" t="str" s="2">
         <v>B&amp;R ARM</v>
       </c>
     </row>
@@ -1416,18 +1304,15 @@
         <v>22402958</v>
       </c>
       <c r="D38" t="str" s="2">
-        <v>EXP</v>
+        <v/>
       </c>
       <c r="E38" t="str" s="2">
-        <v/>
-      </c>
-      <c r="F38" t="str" s="2">
         <v>【OCEANIA】TEMPERZONE</v>
       </c>
-      <c r="G38" s="4" t="d">
+      <c r="F38" s="4" t="d">
         <v>2026-10-23T00:00:00.000Z</v>
       </c>
-      <c r="H38" t="str" s="2">
+      <c r="G38" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1442,18 +1327,15 @@
         <v>22402964</v>
       </c>
       <c r="D39" t="str" s="2">
-        <v>EXP</v>
+        <v>中国</v>
       </c>
       <c r="E39" t="str" s="2">
-        <v>中国</v>
-      </c>
-      <c r="F39" t="str" s="2">
         <v>【CHINA】Delta</v>
       </c>
-      <c r="G39" s="4" t="d">
+      <c r="F39" s="4" t="d">
         <v>2026-10-28T00:00:00.000Z</v>
       </c>
-      <c r="H39" t="str" s="2">
+      <c r="G39" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1468,18 +1350,15 @@
         <v>22402965</v>
       </c>
       <c r="D40" t="str" s="2">
-        <v>EXP</v>
+        <v>中国</v>
       </c>
       <c r="E40" t="str" s="2">
-        <v>中国</v>
-      </c>
-      <c r="F40" t="str" s="2">
         <v>【CHINA】Delta</v>
       </c>
-      <c r="G40" s="4" t="d">
+      <c r="F40" s="4" t="d">
         <v>2026-10-28T00:00:00.000Z</v>
       </c>
-      <c r="H40" t="str" s="2">
+      <c r="G40" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1494,18 +1373,15 @@
         <v>22402966</v>
       </c>
       <c r="D41" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E41" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F41" t="str" s="2">
         <v>【AAI】Delta</v>
       </c>
-      <c r="G41" s="4" t="d">
+      <c r="F41" s="4" t="d">
         <v>2026-10-30T00:00:00.000Z</v>
       </c>
-      <c r="H41" t="str" s="2">
+      <c r="G41" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1520,18 +1396,15 @@
         <v>22402967</v>
       </c>
       <c r="D42" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E42" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F42" t="str" s="2">
         <v>【AAI】Delta</v>
       </c>
-      <c r="G42" s="4" t="d">
+      <c r="F42" s="4" t="d">
         <v>2026-10-30T00:00:00.000Z</v>
       </c>
-      <c r="H42" t="str" s="2">
+      <c r="G42" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1546,18 +1419,15 @@
         <v>22404201</v>
       </c>
       <c r="D43" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E43" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F43" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G43" s="4" t="d">
+      <c r="F43" s="4" t="d">
         <v>2026-11-04T00:00:00.000Z</v>
       </c>
-      <c r="H43" t="str" s="2">
+      <c r="G43" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -1572,18 +1442,15 @@
         <v>22402968</v>
       </c>
       <c r="D44" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E44" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F44" t="str" s="2">
         <v>【AAI】Delta</v>
       </c>
-      <c r="G44" s="4" t="d">
+      <c r="F44" s="4" t="d">
         <v>2026-11-04T00:00:00.000Z</v>
       </c>
-      <c r="H44" t="str" s="2">
+      <c r="G44" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1598,18 +1465,15 @@
         <v>22402959</v>
       </c>
       <c r="D45" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E45" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F45" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G45" s="4" t="d">
+      <c r="F45" s="4" t="d">
         <v>2026-11-10T00:00:00.000Z</v>
       </c>
-      <c r="H45" t="str" s="2">
+      <c r="G45" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1624,18 +1488,15 @@
         <v>22402960</v>
       </c>
       <c r="D46" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E46" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F46" t="str" s="2">
         <v>ＡＭＡＤＡ　ＣＡＮＡＤＡ　ＬＴＤ．</v>
       </c>
-      <c r="G46" s="4" t="d">
+      <c r="F46" s="4" t="d">
         <v>2026-11-10T00:00:00.000Z</v>
       </c>
-      <c r="H46" t="str" s="2">
+      <c r="G46" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1650,18 +1511,15 @@
         <v>22302248</v>
       </c>
       <c r="D47" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E47" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F47" t="str" s="2">
         <v>（有）共伸テクニカル</v>
       </c>
-      <c r="G47" s="4" t="d">
+      <c r="F47" s="4" t="d">
         <v>2026-11-13T00:00:00.000Z</v>
       </c>
-      <c r="H47" t="str" s="2">
+      <c r="G47" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1676,18 +1534,15 @@
         <v>22302249</v>
       </c>
       <c r="D48" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E48" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F48" t="str" s="2">
         <v>（株）日越工業</v>
       </c>
-      <c r="G48" s="4" t="d">
+      <c r="F48" s="4" t="d">
         <v>2026-11-13T00:00:00.000Z</v>
       </c>
-      <c r="H48" t="str" s="2">
+      <c r="G48" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1702,18 +1557,15 @@
         <v>22402972</v>
       </c>
       <c r="D49" t="str" s="2">
-        <v>EXP</v>
+        <v>ベトナム</v>
       </c>
       <c r="E49" t="str" s="2">
-        <v>ベトナム</v>
-      </c>
-      <c r="F49" t="str" s="2">
         <v>【ベトナム】Foxconnベトナム</v>
       </c>
-      <c r="G49" s="4" t="d">
+      <c r="F49" s="4" t="d">
         <v>2026-11-19T00:00:00.000Z</v>
       </c>
-      <c r="H49" t="str" s="2">
+      <c r="G49" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1728,18 +1580,15 @@
         <v>22404203</v>
       </c>
       <c r="D50" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E50" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F50" t="str" s="2">
         <v>ＡＭＡＤＡ　ＣＡＮＡＤＡ　ＬＴＤ．</v>
       </c>
-      <c r="G50" s="4" t="d">
+      <c r="F50" s="4" t="d">
         <v>2026-11-19T00:00:00.000Z</v>
       </c>
-      <c r="H50" t="str" s="2">
+      <c r="G50" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -1754,18 +1603,15 @@
         <v>22402973</v>
       </c>
       <c r="D51" t="str" s="2">
-        <v>EXP</v>
+        <v>ベトナム</v>
       </c>
       <c r="E51" t="str" s="2">
-        <v>ベトナム</v>
-      </c>
-      <c r="F51" t="str" s="2">
         <v>【ベトナム】Foxconnベトナム</v>
       </c>
-      <c r="G51" s="4" t="d">
+      <c r="F51" s="4" t="d">
         <v>2026-11-24T00:00:00.000Z</v>
       </c>
-      <c r="H51" t="str" s="2">
+      <c r="G51" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1780,18 +1626,15 @@
         <v>22402974</v>
       </c>
       <c r="D52" t="str" s="2">
-        <v>EXP</v>
+        <v>ベトナム</v>
       </c>
       <c r="E52" t="str" s="2">
-        <v>ベトナム</v>
-      </c>
-      <c r="F52" t="str" s="2">
         <v>【ベトナム】Foxconnベトナム</v>
       </c>
-      <c r="G52" s="4" t="d">
+      <c r="F52" s="4" t="d">
         <v>2026-11-24T00:00:00.000Z</v>
       </c>
-      <c r="H52" t="str" s="2">
+      <c r="G52" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1806,18 +1649,15 @@
         <v>22402980</v>
       </c>
       <c r="D53" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E53" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F53" t="str" s="2">
         <v>（株）小山金属</v>
       </c>
-      <c r="G53" s="4" t="d">
+      <c r="F53" s="4" t="d">
         <v>2026-11-27T00:00:00.000Z</v>
       </c>
-      <c r="H53" t="str" s="2">
+      <c r="G53" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1832,18 +1672,15 @@
         <v>22402975</v>
       </c>
       <c r="D54" t="str" s="2">
-        <v>EXP</v>
+        <v>ベトナム</v>
       </c>
       <c r="E54" t="str" s="2">
-        <v>ベトナム</v>
-      </c>
-      <c r="F54" t="str" s="2">
         <v>【ベトナム】Foxconnベトナム</v>
       </c>
-      <c r="G54" s="4" t="d">
+      <c r="F54" s="4" t="d">
         <v>2026-11-27T00:00:00.000Z</v>
       </c>
-      <c r="H54" t="str" s="2">
+      <c r="G54" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1858,18 +1695,15 @@
         <v>22402976</v>
       </c>
       <c r="D55" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E55" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F55" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G55" s="4" t="d">
+      <c r="F55" s="4" t="d">
         <v>2026-12-02T00:00:00.000Z</v>
       </c>
-      <c r="H55" t="str" s="2">
+      <c r="G55" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1884,18 +1718,15 @@
         <v>22402977</v>
       </c>
       <c r="D56" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E56" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F56" t="str" s="2">
         <v>ＡＭＡＤＡ　ＣＡＮＡＤＡ　ＬＴＤ．</v>
       </c>
-      <c r="G56" s="4" t="d">
+      <c r="F56" s="4" t="d">
         <v>2026-12-02T00:00:00.000Z</v>
       </c>
-      <c r="H56" t="str" s="2">
+      <c r="G56" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1910,18 +1741,15 @@
         <v>17302384</v>
       </c>
       <c r="D57" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E57" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F57" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G57" s="4" t="d">
+      <c r="F57" s="4" t="d">
         <v>2026-12-05T00:00:00.000Z</v>
       </c>
-      <c r="H57" t="str" s="2">
+      <c r="G57" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -1936,18 +1764,15 @@
         <v>22404202</v>
       </c>
       <c r="D58" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E58" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F58" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G58" s="4" t="d">
+      <c r="F58" s="4" t="d">
         <v>2026-12-05T00:00:00.000Z</v>
       </c>
-      <c r="H58" t="str" s="2">
+      <c r="G58" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -1962,18 +1787,15 @@
         <v>22404204</v>
       </c>
       <c r="D59" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E59" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F59" t="str" s="2">
         <v>アマダアメリカ</v>
       </c>
-      <c r="G59" s="4" t="d">
+      <c r="F59" s="4" t="d">
         <v>2026-12-09T00:00:00.000Z</v>
       </c>
-      <c r="H59" t="str" s="2">
+      <c r="G59" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -1988,18 +1810,15 @@
         <v>17302385</v>
       </c>
       <c r="D60" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E60" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F60" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G60" s="4" t="d">
+      <c r="F60" s="4" t="d">
         <v>2026-12-10T00:00:00.000Z</v>
       </c>
-      <c r="H60" t="str" s="2">
+      <c r="G60" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2014,18 +1833,15 @@
         <v>22402978</v>
       </c>
       <c r="D61" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E61" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F61" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G61" s="4" t="d">
+      <c r="F61" s="4" t="d">
         <v>2026-12-10T00:00:00.000Z</v>
       </c>
-      <c r="H61" t="str" s="2">
+      <c r="G61" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2040,18 +1856,15 @@
         <v>22404211</v>
       </c>
       <c r="D62" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E62" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F62" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G62" s="4" t="d">
+      <c r="F62" s="4" t="d">
         <v>2026-12-12T00:00:00.000Z</v>
       </c>
-      <c r="H62" t="str" s="2">
+      <c r="G62" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -2066,18 +1879,15 @@
         <v>22402979</v>
       </c>
       <c r="D63" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E63" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F63" t="str" s="2">
         <v>ＡＭＡＤＡ　ＣＡＮＡＤＡ　ＬＴＤ．</v>
       </c>
-      <c r="G63" s="4" t="d">
+      <c r="F63" s="4" t="d">
         <v>2026-12-15T00:00:00.000Z</v>
       </c>
-      <c r="H63" t="str" s="2">
+      <c r="G63" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2092,18 +1902,15 @@
         <v>17302387</v>
       </c>
       <c r="D64" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E64" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F64" t="str" s="2">
         <v/>
       </c>
-      <c r="G64" s="4" t="d">
+      <c r="F64" s="4" t="d">
         <v>2026-12-16T00:00:00.000Z</v>
       </c>
-      <c r="H64" t="str" s="2">
+      <c r="G64" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2118,18 +1925,15 @@
         <v>17402208</v>
       </c>
       <c r="D65" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E65" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F65" t="str" s="2">
         <v/>
       </c>
-      <c r="G65" s="4" t="d">
+      <c r="F65" s="4" t="d">
         <v>2026-12-18T00:00:00.000Z</v>
       </c>
-      <c r="H65" t="str" s="2">
+      <c r="G65" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2144,18 +1948,15 @@
         <v>22402983</v>
       </c>
       <c r="D66" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E66" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F66" t="str" s="2">
         <v/>
       </c>
-      <c r="G66" s="4" t="d">
+      <c r="F66" s="4" t="d">
         <v>2026-12-22T00:00:00.000Z</v>
       </c>
-      <c r="H66" t="str" s="2">
+      <c r="G66" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2170,18 +1971,15 @@
         <v>22402984</v>
       </c>
       <c r="D67" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E67" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F67" t="str" s="2">
         <v/>
       </c>
-      <c r="G67" s="4" t="d">
+      <c r="F67" s="4" t="d">
         <v>2026-12-24T00:00:00.000Z</v>
       </c>
-      <c r="H67" t="str" s="2">
+      <c r="G67" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2196,18 +1994,15 @@
         <v>22404210</v>
       </c>
       <c r="D68" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E68" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F68" t="str" s="2">
         <v>（株）大明</v>
       </c>
-      <c r="G68" s="4" t="d">
+      <c r="F68" s="4" t="d">
         <v>2026-12-26T00:00:00.000Z</v>
       </c>
-      <c r="H68" t="str" s="2">
+      <c r="G68" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -2222,18 +2017,15 @@
         <v>22402981</v>
       </c>
       <c r="D69" t="str" s="2">
-        <v>EXP</v>
+        <v>台湾</v>
       </c>
       <c r="E69" t="str" s="2">
         <v>台湾</v>
       </c>
-      <c r="F69" t="str" s="2">
-        <v>台湾</v>
-      </c>
-      <c r="G69" s="4" t="d">
+      <c r="F69" s="4" t="d">
         <v>2027-01-05T00:00:00.000Z</v>
       </c>
-      <c r="H69" t="str" s="2">
+      <c r="G69" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2248,18 +2040,15 @@
         <v>22402982</v>
       </c>
       <c r="D70" t="str" s="2">
-        <v>EXP</v>
+        <v>中国</v>
       </c>
       <c r="E70" t="str" s="2">
-        <v>中国</v>
-      </c>
-      <c r="F70" t="str" s="2">
         <v>【CHINA】北京埃鉑精密</v>
       </c>
-      <c r="G70" s="4" t="d">
+      <c r="F70" s="4" t="d">
         <v>2027-01-07T00:00:00.000Z</v>
       </c>
-      <c r="H70" t="str" s="2">
+      <c r="G70" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2274,18 +2063,15 @@
         <v>22402986</v>
       </c>
       <c r="D71" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E71" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F71" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G71" s="4" t="d">
+      <c r="F71" s="4" t="d">
         <v>2027-01-09T00:00:00.000Z</v>
       </c>
-      <c r="H71" t="str" s="2">
+      <c r="G71" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2300,18 +2086,15 @@
         <v>22402987</v>
       </c>
       <c r="D72" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E72" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F72" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G72" s="4" t="d">
+      <c r="F72" s="4" t="d">
         <v>2027-01-13T00:00:00.000Z</v>
       </c>
-      <c r="H72" t="str" s="2">
+      <c r="G72" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2326,18 +2109,15 @@
         <v>22404206</v>
       </c>
       <c r="D73" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E73" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F73" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G73" s="4" t="d">
+      <c r="F73" s="4" t="d">
         <v>2027-01-13T00:00:00.000Z</v>
       </c>
-      <c r="H73" t="str" s="2">
+      <c r="G73" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -2352,18 +2132,15 @@
         <v>22302250</v>
       </c>
       <c r="D74" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E74" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F74" t="str" s="2">
         <v>筑波工業（株）</v>
       </c>
-      <c r="G74" s="4" t="d">
+      <c r="F74" s="4" t="d">
         <v>2027-01-15T00:00:00.000Z</v>
       </c>
-      <c r="H74" t="str" s="2">
+      <c r="G74" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2378,18 +2155,15 @@
         <v>22404207</v>
       </c>
       <c r="D75" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E75" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F75" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G75" s="4" t="d">
+      <c r="F75" s="4" t="d">
         <v>2027-01-15T00:00:00.000Z</v>
       </c>
-      <c r="H75" t="str" s="2">
+      <c r="G75" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -2404,18 +2178,15 @@
         <v>17302386</v>
       </c>
       <c r="D76" t="str" s="2">
-        <v>EXP</v>
+        <v>カナダ</v>
       </c>
       <c r="E76" t="str" s="2">
-        <v>カナダ</v>
-      </c>
-      <c r="F76" t="str" s="2">
         <v>【ACL】Greidy Labs</v>
       </c>
-      <c r="G76" s="4" t="d">
+      <c r="F76" s="4" t="d">
         <v>2027-01-19T00:00:00.000Z</v>
       </c>
-      <c r="H76" t="str" s="2">
+      <c r="G76" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2430,18 +2201,15 @@
         <v>22404205</v>
       </c>
       <c r="D77" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E77" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F77" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G77" s="4" t="d">
+      <c r="F77" s="4" t="d">
         <v>2027-01-20T00:00:00.000Z</v>
       </c>
-      <c r="H77" t="str" s="2">
+      <c r="G77" t="str" s="2">
         <v>Y化 Σ10 ATC</v>
       </c>
     </row>
@@ -2456,18 +2224,15 @@
         <v>17302382</v>
       </c>
       <c r="D78" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E78" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F78" t="str" s="2">
         <v>東京キデン（株）</v>
       </c>
-      <c r="G78" s="4" t="d">
+      <c r="F78" s="4" t="d">
         <v>2027-01-22T00:00:00.000Z</v>
       </c>
-      <c r="H78" t="str" s="2">
+      <c r="G78" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2482,18 +2247,15 @@
         <v>17302388</v>
       </c>
       <c r="D79" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E79" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F79" t="str" s="2">
         <v/>
       </c>
-      <c r="G79" s="4" t="d">
+      <c r="F79" s="4" t="d">
         <v>2027-01-23T00:00:00.000Z</v>
       </c>
-      <c r="H79" t="str" s="2">
+      <c r="G79" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2508,18 +2270,15 @@
         <v>22402996</v>
       </c>
       <c r="D80" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E80" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F80" t="str" s="2">
         <v/>
       </c>
-      <c r="G80" s="4" t="d">
+      <c r="F80" s="4" t="d">
         <v>2027-01-27T00:00:00.000Z</v>
       </c>
-      <c r="H80" t="str" s="2">
+      <c r="G80" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2534,18 +2293,15 @@
         <v>22402997</v>
       </c>
       <c r="D81" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E81" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F81" t="str" s="2">
         <v/>
       </c>
-      <c r="G81" s="4" t="d">
+      <c r="F81" s="4" t="d">
         <v>2027-01-29T00:00:00.000Z</v>
       </c>
-      <c r="H81" t="str" s="2">
+      <c r="G81" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2560,18 +2316,15 @@
         <v>22402988</v>
       </c>
       <c r="D82" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E82" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F82" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G82" s="4" t="d">
+      <c r="F82" s="4" t="d">
         <v>2027-02-02T00:00:00.000Z</v>
       </c>
-      <c r="H82" t="str" s="2">
+      <c r="G82" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2586,18 +2339,15 @@
         <v>22402989</v>
       </c>
       <c r="D83" t="str" s="2">
-        <v>EXP</v>
+        <v>米国</v>
       </c>
       <c r="E83" t="str" s="2">
-        <v>米国</v>
-      </c>
-      <c r="F83" t="str" s="2">
         <v>ＡＭＡＤＡ　ＡＭＥＲＩＣＡ　ＩＮＣ．</v>
       </c>
-      <c r="G83" s="4" t="d">
+      <c r="F83" s="4" t="d">
         <v>2027-02-03T00:00:00.000Z</v>
       </c>
-      <c r="H83" t="str" s="2">
+      <c r="G83" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2612,18 +2362,15 @@
         <v>17302389</v>
       </c>
       <c r="D84" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E84" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F84" t="str" s="2">
         <v/>
       </c>
-      <c r="G84" s="4" t="d">
+      <c r="F84" s="4" t="d">
         <v>2027-02-05T00:00:00.000Z</v>
       </c>
-      <c r="H84" t="str" s="2">
+      <c r="G84" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2638,18 +2385,15 @@
         <v>17402209</v>
       </c>
       <c r="D85" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E85" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F85" t="str" s="2">
         <v/>
       </c>
-      <c r="G85" s="4" t="d">
+      <c r="F85" s="4" t="d">
         <v>2027-02-09T00:00:00.000Z</v>
       </c>
-      <c r="H85" t="str" s="2">
+      <c r="G85" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2664,18 +2408,15 @@
         <v>22302251</v>
       </c>
       <c r="D86" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E86" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F86" t="str" s="2">
         <v/>
       </c>
-      <c r="G86" s="4" t="d">
+      <c r="F86" s="4" t="d">
         <v>2027-02-12T00:00:00.000Z</v>
       </c>
-      <c r="H86" t="str" s="2">
+      <c r="G86" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
@@ -2690,30 +2431,27 @@
         <v>22302252</v>
       </c>
       <c r="D87" t="str" s="2">
-        <v>DMS</v>
+        <v>日本</v>
       </c>
       <c r="E87" t="str" s="2">
-        <v>日本</v>
-      </c>
-      <c r="F87" t="str" s="2">
         <v/>
       </c>
-      <c r="G87" s="4" t="d">
+      <c r="F87" s="4" t="d">
         <v>2027-02-13T00:00:00.000Z</v>
       </c>
-      <c r="H87" t="str" s="2">
+      <c r="G87" t="str" s="2">
         <v>Y化 Σ10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H87"/>
+  <autoFilter ref="A1:G87"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G87"/>
   </ignoredErrors>
 </worksheet>
 </file>